--- a/WorkBot/refactor-experimental/data/orders/Coffee Depot LLC/Coffee Depot LLC_Easthill_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Coffee Depot LLC/Coffee Depot LLC_Easthill_20260306.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,33 +447,16 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Monin - Peppermint</t>
+          <t>Monin - Toffee Nut</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Monin - Toffee Nut</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
         <v>0</v>
       </c>
     </row>
